--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1304-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1304-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B0B9E0-3D41-4B0B-9E8D-3E0E6975A879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0767723C-5F87-4F7C-BA6F-1E4166D2767D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{ECC0690F-E6BD-46C9-909D-8957B22020DD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1D7B8043-3B80-4362-A3F1-347A1A98FACB}"/>
   </bookViews>
   <sheets>
     <sheet name="1304-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1601,29 +1601,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8171B76B-2EE1-4004-AE36-54D01322521B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3264C5F1-44A9-4C42-983B-F6F96EC57F63}">
   <dimension ref="A1:X54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1657,7 +1656,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1693,7 +1692,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1745,7 +1744,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1813,7 +1812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1885,7 +1884,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2029,7 +2028,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2101,7 +2100,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2173,7 +2172,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2245,7 +2244,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2317,7 +2316,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2389,7 +2388,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2461,7 +2460,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2533,7 +2532,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2605,7 +2604,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2749,7 +2748,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2821,7 +2820,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2965,7 +2964,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3037,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3109,7 +3108,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3181,7 +3180,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3253,7 +3252,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3325,7 +3324,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3397,7 +3396,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2002</v>
       </c>
@@ -3469,7 +3468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2001</v>
       </c>
@@ -3541,7 +3540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2000</v>
       </c>
@@ -3613,7 +3612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>1999</v>
       </c>
@@ -3685,7 +3684,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1998</v>
       </c>
@@ -3757,7 +3756,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>1997</v>
       </c>
@@ -3829,7 +3828,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42">
         <v>1996</v>
       </c>
@@ -3901,7 +3900,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="44"/>
       <c r="B34" s="45"/>
       <c r="C34" s="19" t="s">
@@ -3929,7 +3928,7 @@
       <c r="W34" s="51"/>
       <c r="X34" s="47"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>1995</v>
       </c>
@@ -4001,7 +4000,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>1994</v>
       </c>
@@ -4073,7 +4072,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="44"/>
       <c r="B37" s="45"/>
       <c r="C37" s="19" t="s">
@@ -4101,7 +4100,7 @@
       <c r="W37" s="51"/>
       <c r="X37" s="47"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52">
         <v>1993</v>
       </c>
@@ -4173,7 +4172,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="54"/>
       <c r="B39" s="55"/>
       <c r="C39" s="21" t="s">
@@ -4201,7 +4200,7 @@
       <c r="W39" s="61"/>
       <c r="X39" s="57"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>1992</v>
       </c>
@@ -4273,7 +4272,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="44"/>
       <c r="B41" s="45"/>
       <c r="C41" s="19" t="s">
@@ -4301,7 +4300,7 @@
       <c r="W41" s="51"/>
       <c r="X41" s="47"/>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="52">
         <v>1991</v>
       </c>
@@ -4373,7 +4372,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="54"/>
       <c r="B43" s="55"/>
       <c r="C43" s="21" t="s">
@@ -4401,7 +4400,7 @@
       <c r="W43" s="61"/>
       <c r="X43" s="57"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>1990</v>
       </c>
@@ -4473,7 +4472,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="44"/>
       <c r="B45" s="45"/>
       <c r="C45" s="19" t="s">
@@ -4501,7 +4500,7 @@
       <c r="W45" s="51"/>
       <c r="X45" s="47"/>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="52">
         <v>1989</v>
       </c>
@@ -4573,7 +4572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="54"/>
       <c r="B47" s="55"/>
       <c r="C47" s="21" t="s">
@@ -4601,7 +4600,7 @@
       <c r="W47" s="61"/>
       <c r="X47" s="57"/>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38">
         <v>1988</v>
       </c>
@@ -4673,7 +4672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="40">
         <v>1987</v>
       </c>
@@ -4745,7 +4744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="38">
         <v>1986</v>
       </c>
@@ -4817,7 +4816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="40">
         <v>1985</v>
       </c>
@@ -4889,7 +4888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="38">
         <v>1984</v>
       </c>
@@ -4961,7 +4960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="40">
         <v>1983</v>
       </c>
@@ -5033,7 +5032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="38" t="s">
         <v>68</v>
       </c>
